--- a/src/kcii_audit/resources/questionnaires/templates/security_appliance_questionnaire.xlsx
+++ b/src/kcii_audit/resources/questionnaires/templates/security_appliance_questionnaire.xlsx
@@ -515,27 +515,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>항목ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>interview_topic</t>
+          <t>인터뷰주제</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>answer_summary</t>
+          <t>답변요약</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>evidence_status</t>
+          <t>증적상태</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>validation_warning</t>
+          <t>검증경고</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>항목ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>mapping_rule</t>
+          <t>판정규칙</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>decision_hint</t>
+          <t>판정안내</t>
         </is>
       </c>
     </row>
@@ -1323,19 +1323,19 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>항목</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>값</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>asset_alias</t>
+          <t>비식별 자산명</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>appliance_type</t>
+          <t>보안장비 유형</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -1351,7 +1351,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>evidence_date</t>
+          <t>증적 기준일</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -1359,7 +1359,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>reviewer_role</t>
+          <t>검토자 역할</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -1381,47 +1381,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>항목ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>질문</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>answer_type</t>
+          <t>답변유형</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>required_evidence</t>
+          <t>필요증적</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>options</t>
+          <t>선택지</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>mapping_rule</t>
+          <t>판정규칙</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>답변</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>evidence_status</t>
+          <t>증적상태</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1617,47 +1617,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>항목ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>질문</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>answer_type</t>
+          <t>답변유형</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>required_evidence</t>
+          <t>필요증적</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>options</t>
+          <t>선택지</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>mapping_rule</t>
+          <t>판정규칙</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>답변</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>evidence_status</t>
+          <t>증적상태</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1783,47 +1783,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>항목ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>질문</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>answer_type</t>
+          <t>답변유형</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>required_evidence</t>
+          <t>필요증적</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>options</t>
+          <t>선택지</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>mapping_rule</t>
+          <t>판정규칙</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>답변</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>evidence_status</t>
+          <t>증적상태</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -2019,47 +2019,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>항목ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>질문</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>answer_type</t>
+          <t>답변유형</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>required_evidence</t>
+          <t>필요증적</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>options</t>
+          <t>선택지</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>mapping_rule</t>
+          <t>판정규칙</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>답변</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>evidence_status</t>
+          <t>증적상태</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -2185,47 +2185,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>항목ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>질문</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>answer_type</t>
+          <t>답변유형</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>required_evidence</t>
+          <t>필요증적</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>options</t>
+          <t>선택지</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>mapping_rule</t>
+          <t>판정규칙</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>답변</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>evidence_status</t>
+          <t>증적상태</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -2281,47 +2281,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>항목ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>질문</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>answer_type</t>
+          <t>답변유형</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>required_evidence</t>
+          <t>필요증적</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>options</t>
+          <t>선택지</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>mapping_rule</t>
+          <t>판정규칙</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>답변</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>evidence_status</t>
+          <t>증적상태</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -2377,47 +2377,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>항목ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>질문</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>answer_type</t>
+          <t>답변유형</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>required_evidence</t>
+          <t>필요증적</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>options</t>
+          <t>선택지</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>mapping_rule</t>
+          <t>판정규칙</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>answer</t>
+          <t>답변</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>evidence_status</t>
+          <t>증적상태</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>비고</t>
         </is>
       </c>
     </row>
